--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>178.62</v>
+        <v>212.06</v>
       </c>
       <c r="C2" t="n">
-        <v>145.06</v>
+        <v>167.22</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.54</v>
+        <v>14.34</v>
       </c>
       <c r="C3" t="n">
-        <v>17.2</v>
+        <v>11.83</v>
       </c>
       <c r="D3" t="n">
-        <v>22.31</v>
+        <v>23.21</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>99.52</v>
+        <v>80.16</v>
       </c>
       <c r="C4" t="n">
-        <v>87.05</v>
+        <v>71.08</v>
       </c>
       <c r="D4" t="n">
-        <v>92.73999999999999</v>
+        <v>193.8</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77.43000000000001</v>
+        <v>98.05</v>
       </c>
       <c r="C6" t="n">
-        <v>70.38</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>17.01</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.33</v>
+        <v>3.15</v>
       </c>
       <c r="C9" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="D9" t="n">
-        <v>56.16</v>
+        <v>96.04000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.55</v>
+        <v>11.06</v>
       </c>
       <c r="C10" t="n">
-        <v>11.04</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>37.39</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.47</v>
+        <v>24.04</v>
       </c>
       <c r="C11" t="n">
-        <v>22.69</v>
+        <v>20.98</v>
       </c>
       <c r="D11" t="n">
-        <v>13.5</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.56999999999999</v>
+        <v>169.66</v>
       </c>
       <c r="C12" t="n">
-        <v>68.05</v>
+        <v>150.24</v>
       </c>
       <c r="D12" t="n">
-        <v>8.630000000000001</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="13">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75.55</v>
+        <v>117.46</v>
       </c>
       <c r="C13" t="n">
-        <v>65.54000000000001</v>
+        <v>108.56</v>
       </c>
       <c r="D13" t="n">
-        <v>20.99</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="14">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.19</v>
+        <v>8.42</v>
       </c>
       <c r="C14" t="n">
-        <v>10.45</v>
+        <v>5.55</v>
       </c>
       <c r="D14" t="n">
-        <v>170.24</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="C15" t="n">
         <v>0.26</v>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.99</v>
+        <v>35.54</v>
       </c>
       <c r="C16" t="n">
-        <v>21.02</v>
+        <v>28.26</v>
       </c>
       <c r="D16" t="n">
-        <v>32.66</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="17">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>155.31</v>
+        <v>154.22</v>
       </c>
       <c r="C17" t="n">
-        <v>125.27</v>
+        <v>117.75</v>
       </c>
       <c r="D17" t="n">
-        <v>49.64</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="18">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="C18" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>242.24</v>
+        <v>304.75</v>
       </c>
       <c r="C19" t="n">
-        <v>205.45</v>
+        <v>256.93</v>
       </c>
       <c r="D19" t="n">
-        <v>12.78</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="20">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>471.67</v>
+        <v>430.98</v>
       </c>
       <c r="C20" t="n">
-        <v>420.55</v>
+        <v>389.15</v>
       </c>
       <c r="D20" t="n">
-        <v>28.13</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="21">
@@ -751,12 +751,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="C21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>0.88</v>
+      </c>
+      <c r="D21" t="n">
+        <v>107.47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
